--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:30</t>
+          <t>2026-10-14 14:14:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1727,7 +1727,11 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>( &lt;http://publications.europa.eu/resource/authority/access-right/PUBLIC&gt; &lt;http://publications.europa.eu/resource/authority/access-right/RESTRICTED&gt; &lt;http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC&gt; )</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1739,7 +1743,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dash:URIEditor</t>
+          <t>dash:EnumSelectEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-DataServiceShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-DataServiceShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:49</t>
+          <t>2026-10-14 14:30:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#DataServiceShape</t>
+          <t>http://data.health-ri.nl/core/p2/DataServiceShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:accessRights</t>
+          <t>hrishapes:DataServiceShape#dct:accessRights</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1750,12 +1767,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcatap:applicableLegislation</t>
+          <t>hrishapes:DataServiceShape#dcatap:applicableLegislation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1808,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:conformsTo</t>
+          <t>hrishapes:DataServiceShape#dct:conformsTo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1866,12 +1883,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:contactPoint</t>
+          <t>hrishapes:DataServiceShape#dcat:contactPoint</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1928,12 +1945,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:creator</t>
+          <t>hrishapes:DataServiceShape#dct:creator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1986,12 +2003,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:rights</t>
+          <t>hrishapes:DataServiceShape#dct:rights</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2044,12 +2061,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:description</t>
+          <t>hrishapes:DataServiceShape#dct:description</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2106,12 +2123,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:endpointDescription</t>
+          <t>hrishapes:DataServiceShape#dcat:endpointDescription</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2168,12 +2185,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:endpointURL</t>
+          <t>hrishapes:DataServiceShape#dcat:endpointURL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2230,12 +2247,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:format</t>
+          <t>hrishapes:DataServiceShape#dct:format</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2288,12 +2305,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcatap:hvdCategory</t>
+          <t>hrishapes:DataServiceShape#dcatap:hvdCategory</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2346,12 +2363,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:identifier</t>
+          <t>hrishapes:DataServiceShape#dct:identifier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2408,12 +2425,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:keyword</t>
+          <t>hrishapes:DataServiceShape#dcat:keyword</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2466,12 +2483,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:landingPage</t>
+          <t>hrishapes:DataServiceShape#dcat:landingPage</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2524,12 +2541,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:language</t>
+          <t>hrishapes:DataServiceShape#dct:language</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2582,12 +2599,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:license</t>
+          <t>hrishapes:DataServiceShape#dct:license</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2644,12 +2661,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:modified</t>
+          <t>hrishapes:DataServiceShape#dct:modified</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2712,12 +2729,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/adms:identifier</t>
+          <t>hrishapes:DataServiceShape#adms:identifier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2770,12 +2787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:publisher</t>
+          <t>hrishapes:DataServiceShape#dct:publisher</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2832,12 +2849,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:servesDataset</t>
+          <t>hrishapes:DataServiceShape#dcat:servesDataset</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2890,12 +2907,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dcat:theme</t>
+          <t>hrishapes:DataServiceShape#dcat:theme</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2954,12 +2971,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape/dct:title</t>
+          <t>hrishapes:DataServiceShape#dct:title</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hri:DataServiceShape</t>
+          <t>hrishapes:DataServiceShape</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:38</t>
+          <t>2026-10-19 15:50:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#KindShape</t>
+          <t>http://data.health-ri.nl/core/p2/KindShape</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2587,7 +2587,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2759,7 +2759,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#IdentifierShape</t>
+          <t>http://data.health-ri.nl/core/p2/IdentifierShape</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:03</t>
+          <t>2026-10-26 13:15:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:50</t>
+          <t>2026-10-26 16:19:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:39</t>
+          <t>2026-10-27 15:44:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:13</t>
+          <t>2026-10-28 09:50:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataservice.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:42</t>
+          <t>2026-10-28 11:04:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
